--- a/esyluban/examples/release/DataTables/test/test_index.xlsx
+++ b/esyluban/examples/release/DataTables/test/test_index.xlsx
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4"/>
   <sheetData>
     <row r="1">
@@ -1137,22 +1137,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
